--- a/Nhom01/SE_9/SE_9_Nhom01_AcceptanceCriteria.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_AcceptanceCriteria.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>At least 80% of user stories have acceptance criteria.</t>
+          <t>Ít nhất 80% câu chuyện người dùng có tiêu chí nghiệm thu.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>23 AC rows 2–24; 16 Stories rows 2–17</t>
+          <t>AC-EP001-01–AC-EP005-05; US-001–US-016</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Each criterion is Given–When–Then or checklist and lets a tester decide pass/fail.</t>
+          <t>Mỗi tiêu chí được viết theo dạng Điều kiện – Hành động – Kết quả hoặc danh sách kiểm tra; người kiểm thử xác định được đạt hay không đạt.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Columns C:E, rows 2–24</t>
+          <t>AC-EP001-01–AC-EP005-05</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>The criterion says which current pain the story removes.</t>
+          <t>Tiêu chí nêu rõ vấn đề hiện trạng mà câu chuyện người dùng giải quyết.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–24</t>
+          <t>AC-EP001-01–AC-EP005-05; AS-001–AS-008</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>All criteria for an epic together cover its outcome, not only one screen.</t>
+          <t>Các tiêu chí của mỗi nhóm nghiệp vụ khi xét cùng nhau phải bao quát kết quả của toàn nhóm nghiệp vụ, không chỉ một màn hình.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>AC row 17 (AC-EP004-03); PBI row 21 (PBI-020); User Story row 14 (US-013); PBI rows 2 and 12 (PBI-001/PBI-011); As-Is row 3 (AS-001).</t>
+          <t>AC-EP001-01–AC-EP005-05; AC-EP004-03; PBI-020; US-013; PBI-001; PBI-011; AS-001</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
